--- a/inst/STUDY01_TRAIL01/rules/config/rule_registry.xlsx
+++ b/inst/STUDY01_TRAIL01/rules/config/rule_registry.xlsx
@@ -1564,7 +1564,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>11</v>
       </c>
@@ -1669,7 +1669,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>60</v>
       </c>
@@ -1739,7 +1739,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>60</v>
       </c>
@@ -1774,7 +1774,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>60</v>
       </c>
@@ -1844,7 +1844,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>26</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>26</v>
       </c>
@@ -3315,7 +3315,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/inst/STUDY01_TRAIL01/rules/config/rule_registry.xlsx
+++ b/inst/STUDY01_TRAIL01/rules/config/rule_registry.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180"/>
   </bookViews>
   <sheets>
     <sheet name="Trial" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Study!$A$1:$K$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Trial!$A$1:$K$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Trial!$A$1:$K$51</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -1584,7 +1584,7 @@
         <v>15</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>15</v>
@@ -1680,7 +1680,7 @@
         <v>61</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>14</v>
@@ -1688,8 +1688,8 @@
       <c r="F5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>14</v>
+      <c r="G5" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>14</v>
@@ -1714,8 +1714,8 @@
       <c r="C6" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>14</v>
+      <c r="D6" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>15</v>
@@ -1750,7 +1750,7 @@
         <v>63</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>14</v>
@@ -1758,8 +1758,8 @@
       <c r="F7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>14</v>
+      <c r="G7" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>14</v>
@@ -1784,11 +1784,11 @@
       <c r="C8" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>14</v>
+      <c r="D8" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>14</v>
@@ -1819,8 +1819,8 @@
       <c r="C9" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>14</v>
+      <c r="D9" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>15</v>
@@ -1855,7 +1855,7 @@
         <v>28</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>14</v>
@@ -1863,8 +1863,8 @@
       <c r="F10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>14</v>
+      <c r="G10" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>14</v>
@@ -1889,8 +1889,8 @@
       <c r="C11" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>14</v>
+      <c r="D11" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>15</v>
@@ -1925,7 +1925,7 @@
         <v>36</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>14</v>
@@ -1933,8 +1933,8 @@
       <c r="F12" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>14</v>
+      <c r="G12" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>14</v>
@@ -1960,7 +1960,7 @@
         <v>67</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>14</v>
@@ -1968,8 +1968,8 @@
       <c r="F13" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="8" t="s">
-        <v>14</v>
+      <c r="G13" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>15</v>
@@ -1995,7 +1995,7 @@
         <v>68</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>14</v>
@@ -2030,7 +2030,7 @@
         <v>69</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>14</v>
@@ -2065,7 +2065,7 @@
         <v>71</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>14</v>
@@ -2100,7 +2100,7 @@
         <v>72</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>14</v>
@@ -2135,7 +2135,7 @@
         <v>73</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>14</v>
@@ -2170,7 +2170,7 @@
         <v>75</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>14</v>
@@ -2205,7 +2205,7 @@
         <v>76</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>14</v>
@@ -2240,7 +2240,7 @@
         <v>77</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>14</v>
@@ -2275,7 +2275,7 @@
         <v>78</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>14</v>
@@ -2310,7 +2310,7 @@
         <v>79</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>14</v>
@@ -2345,7 +2345,7 @@
         <v>80</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>14</v>
@@ -2380,7 +2380,7 @@
         <v>82</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>14</v>
@@ -2415,7 +2415,7 @@
         <v>83</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>14</v>
@@ -2450,7 +2450,7 @@
         <v>84</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>14</v>
@@ -2485,7 +2485,7 @@
         <v>86</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>14</v>
@@ -2519,8 +2519,8 @@
       <c r="C29" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="D29" s="8" t="s">
-        <v>14</v>
+      <c r="D29" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>14</v>
@@ -2554,8 +2554,8 @@
       <c r="C30" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D30" s="8" t="s">
-        <v>14</v>
+      <c r="D30" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>14</v>
@@ -2589,8 +2589,8 @@
       <c r="C31" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D31" s="8" t="s">
-        <v>14</v>
+      <c r="D31" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>14</v>
@@ -2624,8 +2624,8 @@
       <c r="C32" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D32" s="8" t="s">
-        <v>14</v>
+      <c r="D32" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>14</v>
@@ -2659,8 +2659,8 @@
       <c r="C33" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D33" s="8" t="s">
-        <v>14</v>
+      <c r="D33" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>14</v>
@@ -2694,8 +2694,8 @@
       <c r="C34" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D34" s="8" t="s">
-        <v>14</v>
+      <c r="D34" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>14</v>
@@ -2729,8 +2729,8 @@
       <c r="C35" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D35" s="8" t="s">
-        <v>14</v>
+      <c r="D35" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>14</v>
@@ -2764,8 +2764,8 @@
       <c r="C36" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D36" s="8" t="s">
-        <v>14</v>
+      <c r="D36" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>14</v>
@@ -2799,8 +2799,8 @@
       <c r="C37" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D37" s="8" t="s">
-        <v>14</v>
+      <c r="D37" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>14</v>
@@ -2834,8 +2834,8 @@
       <c r="C38" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="D38" s="8" t="s">
-        <v>14</v>
+      <c r="D38" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>14</v>
@@ -2869,8 +2869,8 @@
       <c r="C39" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="D39" s="8" t="s">
-        <v>14</v>
+      <c r="D39" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>14</v>
@@ -2904,8 +2904,8 @@
       <c r="C40" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="D40" s="8" t="s">
-        <v>14</v>
+      <c r="D40" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>14</v>
@@ -2939,8 +2939,8 @@
       <c r="C41" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="D41" s="8" t="s">
-        <v>14</v>
+      <c r="D41" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>14</v>
@@ -2974,8 +2974,8 @@
       <c r="C42" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D42" s="8" t="s">
-        <v>14</v>
+      <c r="D42" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>14</v>
@@ -3009,8 +3009,8 @@
       <c r="C43" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="D43" s="8" t="s">
-        <v>14</v>
+      <c r="D43" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>14</v>
@@ -3044,8 +3044,8 @@
       <c r="C44" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D44" s="8" t="s">
-        <v>14</v>
+      <c r="D44" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>14</v>
@@ -3079,8 +3079,8 @@
       <c r="C45" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="D45" s="8" t="s">
-        <v>14</v>
+      <c r="D45" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>14</v>
@@ -3114,8 +3114,8 @@
       <c r="C46" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D46" s="8" t="s">
-        <v>14</v>
+      <c r="D46" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>14</v>
@@ -3149,8 +3149,8 @@
       <c r="C47" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="D47" s="8" t="s">
-        <v>14</v>
+      <c r="D47" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>14</v>
@@ -3184,8 +3184,8 @@
       <c r="C48" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D48" s="8" t="s">
-        <v>14</v>
+      <c r="D48" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>14</v>
@@ -3219,8 +3219,8 @@
       <c r="C49" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="D49" s="8" t="s">
-        <v>14</v>
+      <c r="D49" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E49" s="6" t="s">
         <v>14</v>
@@ -3254,8 +3254,8 @@
       <c r="C50" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="D50" s="8" t="s">
-        <v>14</v>
+      <c r="D50" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>14</v>
@@ -3289,8 +3289,8 @@
       <c r="C51" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="D51" s="8" t="s">
-        <v>14</v>
+      <c r="D51" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>14</v>
@@ -3315,6 +3315,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3488,7 +3489,7 @@
         <v>213</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>14</v>
@@ -3522,8 +3523,8 @@
       <c r="C6" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>14</v>
+      <c r="D6" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>14</v>
@@ -3558,7 +3559,7 @@
         <v>219</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>14</v>
@@ -3593,7 +3594,7 @@
         <v>50</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>14</v>
@@ -3627,8 +3628,8 @@
       <c r="C9" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>14</v>
+      <c r="D9" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
@@ -3663,7 +3664,7 @@
         <v>57</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>14</v>
@@ -3687,7 +3688,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>66</v>
       </c>
@@ -3698,7 +3699,7 @@
         <v>222</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>14</v>
@@ -3722,7 +3723,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>66</v>
       </c>
@@ -3733,7 +3734,7 @@
         <v>223</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>14</v>
@@ -3757,7 +3758,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>66</v>
       </c>
@@ -3768,7 +3769,7 @@
         <v>224</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>14</v>
@@ -3803,7 +3804,7 @@
         <v>225</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>14</v>
@@ -3838,7 +3839,7 @@
         <v>226</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>14</v>
@@ -3873,7 +3874,7 @@
         <v>227</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>14</v>
@@ -3897,7 +3898,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>74</v>
       </c>
@@ -3908,7 +3909,7 @@
         <v>228</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>14</v>
@@ -3932,7 +3933,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>74</v>
       </c>
@@ -3943,7 +3944,7 @@
         <v>229</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>14</v>
@@ -3967,7 +3968,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>74</v>
       </c>
@@ -3978,7 +3979,7 @@
         <v>230</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>14</v>
@@ -4013,7 +4014,7 @@
         <v>231</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>14</v>
@@ -4048,7 +4049,7 @@
         <v>232</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>14</v>
@@ -4083,7 +4084,7 @@
         <v>233</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>14</v>
@@ -4118,7 +4119,7 @@
         <v>234</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E23" s="8" t="s">
         <v>14</v>
@@ -4153,7 +4154,7 @@
         <v>235</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>14</v>
@@ -4188,7 +4189,7 @@
         <v>236</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E25" s="8" t="s">
         <v>14</v>
@@ -4223,7 +4224,7 @@
         <v>237</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E26" s="8" t="s">
         <v>14</v>
@@ -4258,7 +4259,7 @@
         <v>238</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E27" s="8" t="s">
         <v>14</v>
@@ -4293,7 +4294,7 @@
         <v>239</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E28" s="8" t="s">
         <v>14</v>
@@ -4328,7 +4329,7 @@
         <v>240</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E29" s="8" t="s">
         <v>14</v>
@@ -4363,7 +4364,7 @@
         <v>241</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E30" s="8" t="s">
         <v>14</v>
@@ -4398,7 +4399,7 @@
         <v>242</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E31" s="8" t="s">
         <v>14</v>
@@ -4433,7 +4434,7 @@
         <v>243</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E32" s="8" t="s">
         <v>14</v>
@@ -4468,7 +4469,7 @@
         <v>245</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E33" s="8" t="s">
         <v>14</v>
@@ -4503,7 +4504,7 @@
         <v>246</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E34" s="8" t="s">
         <v>14</v>
@@ -4538,7 +4539,7 @@
         <v>247</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E35" s="8" t="s">
         <v>14</v>
@@ -4573,7 +4574,7 @@
         <v>248</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E36" s="8" t="s">
         <v>14</v>
@@ -4608,7 +4609,7 @@
         <v>249</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E37" s="8" t="s">
         <v>14</v>
@@ -4643,7 +4644,7 @@
         <v>250</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E38" s="8" t="s">
         <v>14</v>
@@ -4678,7 +4679,7 @@
         <v>251</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E39" s="8" t="s">
         <v>14</v>
@@ -4713,7 +4714,7 @@
         <v>252</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E40" s="8" t="s">
         <v>14</v>
@@ -4748,7 +4749,7 @@
         <v>253</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E41" s="8" t="s">
         <v>14</v>
@@ -4783,7 +4784,7 @@
         <v>254</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E42" s="8" t="s">
         <v>14</v>
@@ -4818,7 +4819,7 @@
         <v>255</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E43" s="8" t="s">
         <v>14</v>
@@ -4853,7 +4854,7 @@
         <v>256</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E44" s="8" t="s">
         <v>14</v>
@@ -4888,7 +4889,7 @@
         <v>257</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E45" s="8" t="s">
         <v>14</v>
@@ -4923,7 +4924,7 @@
         <v>258</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E46" s="8" t="s">
         <v>14</v>
@@ -4958,7 +4959,7 @@
         <v>259</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E47" s="8" t="s">
         <v>14</v>
@@ -4993,7 +4994,7 @@
         <v>260</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E48" s="8" t="s">
         <v>14</v>
@@ -5028,7 +5029,7 @@
         <v>261</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E49" s="8" t="s">
         <v>14</v>

--- a/inst/STUDY01_TRAIL01/rules/config/rule_registry.xlsx
+++ b/inst/STUDY01_TRAIL01/rules/config/rule_registry.xlsx
@@ -3315,7 +3315,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
